--- a/artfynd/A 193-2022 artfynd.xlsx
+++ b/artfynd/A 193-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 193-2022 artfynd.xlsx
+++ b/artfynd/A 193-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111485382</v>
+        <v>111619674</v>
       </c>
       <c r="B2" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,53 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Avverkningsanmäld skog Nisshyttan, Dlr</t>
+          <t>Tommus fäbodar, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535326.6336228757</v>
+        <v>535428</v>
       </c>
       <c r="R2" t="n">
-        <v>6679442.236987636</v>
+        <v>6679480</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Kull med talltita som födosökte i tallskogen</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,37 +757,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Dalin</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Dalin</t>
+          <t>Stig-Åke Svenson, Cecilia Rastad, Åke Persson, Peter Dalin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111619716</v>
+        <v>111619684</v>
       </c>
       <c r="B3" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -851,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535380.5123938145</v>
+        <v>535421</v>
       </c>
       <c r="R3" t="n">
-        <v>6679476.022363457</v>
+        <v>6679487</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,19 +847,9 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111619674</v>
+        <v>111619716</v>
       </c>
       <c r="B4" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -967,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535428.2196566191</v>
+        <v>535380</v>
       </c>
       <c r="R4" t="n">
-        <v>6679479.463591517</v>
+        <v>6679476</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,19 +948,9 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,56 +978,64 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111619684</v>
+        <v>111485382</v>
       </c>
       <c r="B5" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tommus fäbodar, Dlr</t>
+          <t>Avverkningsanmäld skog Nisshyttan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535421.1907486108</v>
+        <v>535327</v>
       </c>
       <c r="R5" t="n">
-        <v>6679486.346057601</v>
+        <v>6679443</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,22 +1059,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kull med talltita som födosökte i tallskogen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,19 +1088,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Peter Dalin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson, Cecilia Rastad, Åke Persson, Peter Dalin</t>
+          <t>Peter Dalin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 193-2022 artfynd.xlsx
+++ b/artfynd/A 193-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111619674</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111619684</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111619716</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,8 +1123,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111485382</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>